--- a/data/trans_bre/P16A05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A05-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,51</t>
+          <t>1,7; 5,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 7,98</t>
+          <t>3,38; 8,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,4</t>
+          <t>4,95; 10,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,73; 13,04</t>
+          <t>6,34; 12,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,36; 146,83</t>
+          <t>30,41; 152,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,1; 194,25</t>
+          <t>49,18; 206,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,68; 266,62</t>
+          <t>76,26; 265,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60,4; 189,85</t>
+          <t>59,2; 189,67</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,32</t>
+          <t>1,26; 3,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,92</t>
+          <t>1,32; 4,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,82</t>
+          <t>2,04; 4,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,09</t>
+          <t>0,44; 3,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,15; 311,46</t>
+          <t>61,99; 325,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,13; 202,0</t>
+          <t>41,55; 201,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,57; 179,37</t>
+          <t>51,04; 178,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,96; 146,48</t>
+          <t>12,93; 141,52</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,31</t>
+          <t>-1,78; 2,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 2,84</t>
+          <t>-2,39; 2,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,57</t>
+          <t>-2,21; 1,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,53</t>
+          <t>-0,87; 2,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,58; 147,56</t>
+          <t>-55,76; 144,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,04; 152,49</t>
+          <t>-51,11; 142,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-62,89; 94,92</t>
+          <t>-61,17; 102,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,37; 148,48</t>
+          <t>-27,24; 147,39</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,67</t>
+          <t>1,74; 3,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,99</t>
+          <t>2,67; 4,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,17</t>
+          <t>2,92; 5,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,26</t>
+          <t>2,4; 5,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,93; 164,74</t>
+          <t>58,49; 167,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,27; 168,77</t>
+          <t>67,93; 169,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,25; 171,33</t>
+          <t>76,04; 177,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,23; 158,04</t>
+          <t>52,32; 154,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A05-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>9,26</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>113,21%</t>
+          <t>111,64%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,6</t>
+          <t>1,74; 5,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 8,1</t>
+          <t>3,47; 8,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 10,42</t>
+          <t>4,62; 10,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 12,93</t>
+          <t>6,17; 11,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,41; 152,96</t>
+          <t>30,6; 153,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,18; 206,56</t>
+          <t>49,64; 205,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,26; 265,65</t>
+          <t>69,74; 256,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,2; 189,67</t>
+          <t>59,9; 183,31</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>72,63%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,41</t>
+          <t>1,23; 3,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,01</t>
+          <t>1,28; 4,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,67</t>
+          <t>2,07; 4,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,95</t>
+          <t>1,64; 4,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,99; 325,24</t>
+          <t>62,43; 337,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,55; 201,04</t>
+          <t>40,02; 197,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,04; 178,68</t>
+          <t>53,96; 187,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 141,52</t>
+          <t>34,83; 125,07</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,37</t>
+          <t>-1,57; 2,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 2,79</t>
+          <t>-2,27; 3,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,73</t>
+          <t>-2,4; 1,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,35</t>
+          <t>-0,49; 2,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 144,03</t>
+          <t>-52,87; 153,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 142,2</t>
+          <t>-52,04; 176,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-61,17; 102,37</t>
+          <t>-61,86; 109,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 147,39</t>
+          <t>-18,81; 165,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,85</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,64</t>
+          <t>1,76; 3,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,9</t>
+          <t>2,64; 4,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,27</t>
+          <t>3,03; 5,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,16</t>
+          <t>3,02; 5,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,49; 167,3</t>
+          <t>58,07; 164,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,93; 169,72</t>
+          <t>65,67; 171,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,04; 177,49</t>
+          <t>75,54; 170,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,32; 154,66</t>
+          <t>62,07; 132,92</t>
         </is>
       </c>
     </row>
